--- a/docs/cyclicalwaves-custom-filtering-tickers.xlsx
+++ b/docs/cyclicalwaves-custom-filtering-tickers.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\TahlilApp-AI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAACD1B-2F7E-435A-AB3C-60F8067032BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015DA7D2-A924-461B-8525-DE09F5B1813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{09787CA6-779A-4914-85A1-C23971056FDE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CyclicalWaves" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -542,23 +542,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BD36E0-E270-41AC-9B71-7C9A67D0CF0C}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -566,7 +566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -574,7 +574,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -582,7 +582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -590,7 +590,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -598,7 +598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -606,7 +606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -614,7 +614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -622,7 +622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -630,7 +630,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -638,7 +638,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="15" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -654,7 +654,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="16" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -662,7 +662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="17" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -670,7 +670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="18" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -678,7 +678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="20.65" x14ac:dyDescent="1.1499999999999999">
+    <row r="19" spans="1:2" ht="21" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>15</v>
       </c>

--- a/docs/cyclicalwaves-custom-filtering-tickers.xlsx
+++ b/docs/cyclicalwaves-custom-filtering-tickers.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\TahlilApp-AI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015DA7D2-A924-461B-8525-DE09F5B1813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2D7F9C-72FE-4C0F-B2AB-CBD0FAD27D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{09787CA6-779A-4914-85A1-C23971056FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="CyclicalWaves" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -692,4 +693,13 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7626D61-A41C-433C-9A05-4EAA5A6B74BE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>